--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487511_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487511_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.578799999999999</v>
+        <v>7.3419</v>
       </c>
       <c r="E2" t="n">
-        <v>8.511900000000001</v>
+        <v>7.4621</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0669</v>
+        <v>-0.1202</v>
       </c>
       <c r="G2" t="n">
         <v>5.5353</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>2.593</v>
+        <v>1.3561</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6742</v>
+        <v>1.6244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.2683</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3329</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6348</v>
+        <v>4.4111</v>
       </c>
       <c r="E3" t="n">
-        <v>5.099</v>
+        <v>5.625</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4642</v>
+        <v>-1.2139</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4113</v>
+        <v>-2.3953</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1933</v>
+        <v>-3.8257</v>
       </c>
       <c r="I3" t="n">
-        <v>1.218</v>
+        <v>1.4305</v>
       </c>
       <c r="J3" t="n">
-        <v>3.28</v>
+        <v>-0.0485</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5025</v>
+        <v>-1.5842</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7775</v>
+        <v>1.5358</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8687</v>
+        <v>-2.3468</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3092</v>
+        <v>-2.2415</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4405</v>
+        <v>-0.1053</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3709</v>
+        <v>-3.3294</v>
       </c>
       <c r="R3" t="n">
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4389</v>
+        <v>1.8397</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1461</v>
+        <v>1.7609</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2928</v>
+        <v>0.0788</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3905</v>
+        <v>5.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0438</v>
+        <v>7.242</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4344</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2804</v>
+        <v>4.3354</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3874</v>
+        <v>4.9867</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.107</v>
+        <v>-0.6513</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3953</v>
+        <v>1.4113</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.8257</v>
+        <v>0.1933</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4305</v>
+        <v>1.218</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0485</v>
+        <v>3.28</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5842</v>
+        <v>2.5025</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5358</v>
+        <v>0.7775</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3468</v>
+        <v>-1.8687</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2415</v>
+        <v>-2.3092</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1053</v>
+        <v>0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.3294</v>
+        <v>-1.3709</v>
       </c>
       <c r="R4" t="n">
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>1.709</v>
+        <v>2.1395</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5233</v>
+        <v>2.0338</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1857</v>
+        <v>0.1057</v>
       </c>
       <c r="V4" t="n">
-        <v>5.7501</v>
+        <v>-0.3905</v>
       </c>
       <c r="W4" t="n">
-        <v>7.242</v>
+        <v>1.0438</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.492</v>
+        <v>-1.4344</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6677</v>
+        <v>2.5995</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1143</v>
+        <v>2.966</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4467</v>
+        <v>-0.3665</v>
       </c>
       <c r="G5" t="n">
         <v>0.6674</v>
@@ -844,13 +844,13 @@
         <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2371</v>
+        <v>0.6947</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0371</v>
+        <v>0.8146</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2</v>
+        <v>-0.1198</v>
       </c>
       <c r="V5" t="n">
         <v>1.8249</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.995</v>
+        <v>1.9881</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2465</v>
+        <v>1.7317</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2515</v>
+        <v>0.2563</v>
       </c>
       <c r="G6" t="n">
         <v>0.7671</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0528</v>
+        <v>1.0459</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5858</v>
+        <v>1.071</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.533</v>
+        <v>-0.0251</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7102</v>
+        <v>-4.3214</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.1298</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1381</v>
+        <v>-4.1916</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9622</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5101</v>
+        <v>0.899</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4382</v>
+        <v>0.8804</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0415</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5589</v>
+        <v>-4.9819</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1472</v>
+        <v>-2.5168</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4117</v>
+        <v>-2.4651</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6811</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0356</v>
+        <v>0.5414</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.22</v>
+        <v>0.4105</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1843</v>
+        <v>0.1309</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.3971</v>
+        <v>11.8822</v>
       </c>
       <c r="E11" t="n">
-        <v>18.6806</v>
+        <v>20.1657</v>
       </c>
       <c r="F11" t="n">
         <v>-8.2836</v>
@@ -1312,13 +1312,13 @@
         <v>12.7299</v>
       </c>
       <c r="S11" t="n">
-        <v>7.0311</v>
+        <v>8.516299999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>7.1105</v>
+        <v>8.595600000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07940000000000005</v>
+        <v>-0.07930000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>1.7098</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3007</v>
+        <v>4.4683</v>
       </c>
       <c r="E12" t="n">
-        <v>3.323</v>
+        <v>2.402</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9777</v>
+        <v>2.0663</v>
       </c>
       <c r="G12" t="n">
         <v>1.3172</v>
@@ -1390,13 +1390,13 @@
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1218</v>
+        <v>0.2894</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1733</v>
+        <v>0.2523</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0515</v>
+        <v>0.0371</v>
       </c>
       <c r="V12" t="n">
         <v>1.8825</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7737</v>
+        <v>3.033</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7865</v>
+        <v>5.5029</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0129</v>
+        <v>-2.4699</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5541</v>
@@ -1468,13 +1468,13 @@
         <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9464</v>
+        <v>-0.6871</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9569</v>
+        <v>-0.2406</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9895</v>
+        <v>-0.4465</v>
       </c>
       <c r="V13" t="n">
         <v>3.0991</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0199</v>
+        <v>0.7307</v>
       </c>
       <c r="E14" t="n">
-        <v>1.458</v>
+        <v>1.765</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4381</v>
+        <v>-1.0344</v>
       </c>
       <c r="G14" t="n">
         <v>2.9605</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5074</v>
+        <v>-0.7966</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3805</v>
+        <v>-0.0735</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1269</v>
+        <v>-0.7231</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8249</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9278</v>
+        <v>-0.7436</v>
       </c>
       <c r="E15" t="n">
-        <v>0.293</v>
+        <v>0.9465</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2208</v>
+        <v>-1.6901</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0218</v>
+        <v>-3.1286</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.476</v>
+        <v>-1.8813</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5458</v>
+        <v>-1.2473</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6822</v>
+        <v>-1.1255</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.5241</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6822</v>
+        <v>-0.6014</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3396</v>
+        <v>-2.0031</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.476</v>
+        <v>-1.3572</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1364</v>
+        <v>-0.6459</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>0.427</v>
+        <v>0.1304</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6999</v>
+        <v>-0.0282</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2729</v>
+        <v>0.1587</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>2.1003</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1616</v>
+        <v>-1.0519</v>
       </c>
       <c r="E16" t="n">
         <v>0.5392</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7008</v>
+        <v>-1.5911</v>
       </c>
       <c r="G16" t="n">
         <v>2.3395</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7177</v>
+        <v>-0.608</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1012</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6165</v>
+        <v>-0.5068</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2166</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4913</v>
+        <v>-1.3371</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7418</v>
+        <v>-0.1163</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2331</v>
+        <v>-1.2208</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.1286</v>
+        <v>-1.0218</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8813</v>
+        <v>-0.476</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2473</v>
+        <v>-0.5458</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1255</v>
+        <v>-0.6822</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5241</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6014</v>
+        <v>-0.6822</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0031</v>
+        <v>-0.3396</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3572</v>
+        <v>-0.476</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6459</v>
+        <v>0.1364</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6172</v>
+        <v>0.0176</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2329</v>
+        <v>0.2905</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3843</v>
+        <v>-0.2729</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8837</v>
+        <v>-0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1003</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1889</v>
+        <v>-2.0645</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3684</v>
+        <v>-1.1637</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8205</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.3112</v>
@@ -1858,13 +1858,13 @@
         <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.4748</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1606</v>
+        <v>0.0441</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4387</v>
+        <v>-0.5189</v>
       </c>
       <c r="V18" t="n">
         <v>0.0576</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5663</v>
+        <v>-3.3088</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6457000000000001</v>
+        <v>-3.1897</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.212</v>
+        <v>-0.1191</v>
       </c>
       <c r="G19" t="n">
-        <v>1.283</v>
+        <v>-2.6003</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1069</v>
+        <v>1.1991</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8239</v>
+        <v>-3.7994</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6893</v>
+        <v>-0.9389</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7152</v>
+        <v>2.3511</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.026</v>
+        <v>-3.2899</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4062</v>
+        <v>-1.6615</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6083</v>
+        <v>-1.152</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5095</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3793</v>
+        <v>-0.8456</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3435</v>
+        <v>-0.2923</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7228</v>
+        <v>-0.5533</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0991</v>
+        <v>0.3329</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6498</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6914</v>
+        <v>-3.4759</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1897</v>
+        <v>0.5434</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5018</v>
+        <v>-4.0193</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6003</v>
+        <v>1.283</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1991</v>
+        <v>2.1069</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7994</v>
+        <v>-0.8239</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9389</v>
+        <v>2.6893</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3511</v>
+        <v>2.7152</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2899</v>
+        <v>-0.026</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6615</v>
+        <v>-1.4062</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.152</v>
+        <v>-0.6083</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5095</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1958</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2282</v>
+        <v>-0.2889</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2923</v>
+        <v>0.2411</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9359</v>
+        <v>-0.5301</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3329</v>
+        <v>-3.0991</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3329</v>
+        <v>-3.6498</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4641</v>
+        <v>-3.9183</v>
       </c>
       <c r="E21" t="n">
         <v>1.0543</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.5184</v>
+        <v>-4.9726</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5628</v>
@@ -2092,13 +2092,13 @@
         <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5844</v>
+        <v>-1.0386</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0129</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5715</v>
+        <v>-1.0257</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.3971</v>
+        <v>-7.668100000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>8.2834</v>
+        <v>8.2836</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.6807</v>
+        <v>-15.9517</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6562</v>
@@ -2140,7 +2140,7 @@
         <v>5.1143</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.770499999999999</v>
+        <v>-6.7705</v>
       </c>
       <c r="J22" t="n">
         <v>11.0415</v>
@@ -2155,13 +2155,13 @@
         <v>-12.6978</v>
       </c>
       <c r="N22" t="n">
-        <v>-8.811799999999998</v>
+        <v>-8.8118</v>
       </c>
       <c r="O22" t="n">
         <v>-3.886</v>
       </c>
       <c r="P22" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.73</v>
@@ -2170,13 +2170,13 @@
         <v>12.73</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.0311</v>
+        <v>-4.3022</v>
       </c>
       <c r="T22" t="n">
-        <v>0.07940000000000005</v>
+        <v>0.07929999999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>-7.1105</v>
+        <v>-4.381500000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7097</v>
